--- a/Master/2025_and_2026/JSS1.xlsx
+++ b/Master/2025_and_2026/JSS1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\Master\2025_and_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7B40DC-CD5B-47A4-A452-819DA7642892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1962553A-CEF6-459A-965B-D44BC400C0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F458E774-E180-4573-B856-E2B1C5E83C9C}"/>
   </bookViews>
